--- a/downloads/indicadores/IED/IED_datos.xlsx
+++ b/downloads/indicadores/IED/IED_datos.xlsx
@@ -500,14 +500,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía · Frecuencia: Trimestral · Unidad: Millones de dólares</t>
+          <t>Fuente: Secretaría de Economía / Dirección General de Inversión Extranjera · Frecuencia: Trimestral · Unidad: Millones de dólares</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: — · Fecha de publicación: —</t>
+          <t>URL del boletín / serie: https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum · Fecha de publicación: 26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -675,17 +675,17 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -733,17 +733,17 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -791,17 +791,17 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,17 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1023,17 +1023,17 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1081,17 +1081,17 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1139,17 +1139,17 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1197,17 +1197,17 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1255,17 +1255,17 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1313,17 +1313,17 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1371,17 +1371,17 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1429,17 +1429,17 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1487,17 +1487,17 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1545,17 +1545,17 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1603,17 +1603,17 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1661,17 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1719,17 +1719,17 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1777,17 +1777,17 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26 de mayo de 2026</t>
         </is>
       </c>
     </row>

--- a/downloads/indicadores/IED/IED_datos.xlsx
+++ b/downloads/indicadores/IED/IED_datos.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Nuevas Inversiones</t>
+          <t>Nuevas inversiones</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">

--- a/downloads/indicadores/IED/IED_datos.xlsx
+++ b/downloads/indicadores/IED/IED_datos.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -95,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -105,8 +106,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -473,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -482,10 +485,11 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,7 +502,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: Secretaría de Economía / Dirección General de Inversión Extranjera · Frecuencia: Trimestral · Unidad: Millones de dólares</t>
+          <t>Fuente: Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE · Frecuencia: Trimestral · Unidad: Millones de dólares</t>
         </is>
       </c>
     </row>
@@ -522,7 +526,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>IED total</t>
+          <t>IED acumulada</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -542,20 +546,25 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>Var. anual acumulada</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>Carácter del dato</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>URL del boletín</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Fecha de publicación</t>
         </is>
@@ -582,22 +591,23 @@
       <c r="F6" s="6" t="n">
         <v>2629.401193109997</v>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -612,34 +622,35 @@
       <c r="B7" s="5" t="n">
         <v>44287</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="9" t="n">
         <v>18433.46954255985</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="9" t="n">
         <v>6025.000693990005</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="9" t="n">
         <v>8658.214019469988</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="9" t="n">
         <v>3750.254829099993</v>
       </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -666,22 +677,23 @@
       <c r="F8" s="6" t="n">
         <v>5287.674054709976</v>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -696,34 +708,35 @@
       <c r="B9" s="5" t="n">
         <v>44470</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="9" t="n">
         <v>31621.20435087015</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="9" t="n">
         <v>13825.30166943996</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="9" t="n">
         <v>12213.01206093998</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="9" t="n">
         <v>5582.890620490009</v>
       </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -750,22 +763,23 @@
       <c r="F10" s="6" t="n">
         <v>1376.123655999997</v>
       </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -780,34 +794,35 @@
       <c r="B11" s="5" t="n">
         <v>44652</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="9" t="n">
         <v>27511.62373282995</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="9" t="n">
         <v>11836.52779014</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="9" t="n">
         <v>11655.60546753999</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="9" t="n">
         <v>4019.490475149998</v>
       </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -834,22 +849,23 @@
       <c r="F12" s="6" t="n">
         <v>3575.351644790012</v>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -864,34 +880,35 @@
       <c r="B13" s="5" t="n">
         <v>44835</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="9" t="n">
         <v>35291.61835650035</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="9" t="n">
         <v>16993.09777798016</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="9" t="n">
         <v>16027.79041017376</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="9" t="n">
         <v>2270.730168346636</v>
       </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="inlineStr">
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -918,22 +935,23 @@
       <c r="F14" s="6" t="n">
         <v>999.2940460586948</v>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -948,34 +966,35 @@
       <c r="B15" s="5" t="n">
         <v>45017</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="9" t="n">
         <v>29040.8238745911</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="9" t="n">
         <v>2135.168038952664</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="9" t="n">
         <v>22608.62151171782</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="9" t="n">
         <v>4297.034323920598</v>
       </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -1002,22 +1021,23 @@
       <c r="F16" s="6" t="n">
         <v>5215.003869953881</v>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -1032,34 +1052,35 @@
       <c r="B17" s="5" t="n">
         <v>45200</v>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="9" t="n">
         <v>36058.04377568115</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="9" t="n">
         <v>4817.437436025721</v>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E17" s="9" t="n">
         <v>26630.61271059473</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="9" t="n">
         <v>4609.993629060474</v>
       </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -1086,22 +1107,23 @@
       <c r="F18" s="6" t="n">
         <v>98.5581183642047</v>
       </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -1116,34 +1138,35 @@
       <c r="B19" s="5" t="n">
         <v>45383</v>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="9" t="n">
         <v>31096.32510957158</v>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="9" t="n">
         <v>909.3070721249387</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="9" t="n">
         <v>30287.60301161498</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="9" t="n">
         <v>-100.5849741683989</v>
       </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K19" s="11" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -1170,22 +1193,23 @@
       <c r="F20" s="6" t="n">
         <v>2932.281265655119</v>
       </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -1200,34 +1224,35 @@
       <c r="B21" s="5" t="n">
         <v>45566</v>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="9" t="n">
         <v>36872.42195115965</v>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="9" t="n">
         <v>3168.543654846584</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="9" t="n">
         <v>28710.3148665372</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="9" t="n">
         <v>4993.563429775793</v>
       </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K21" s="11" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -1254,22 +1279,23 @@
       <c r="F22" s="6" t="n">
         <v>3139.80373183581</v>
       </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -1284,34 +1310,35 @@
       <c r="B23" s="5" t="n">
         <v>45748</v>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C23" s="9" t="n">
         <v>34264.56746296593</v>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="9" t="n">
         <v>3148.538441297729</v>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="E23" s="9" t="n">
         <v>28914.10863011177</v>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="9" t="n">
         <v>2201.920391556331</v>
       </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -1338,22 +1365,23 @@
       <c r="F24" s="6" t="n">
         <v>6593.391426507059</v>
       </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -1368,34 +1396,35 @@
       <c r="B25" s="5" t="n">
         <v>45931</v>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="9" t="n">
         <v>40870.76932803365</v>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="9" t="n">
         <v>7377.426584413343</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E25" s="9" t="n">
         <v>27649.33990823308</v>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="9" t="n">
         <v>5844.002835387397</v>
       </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -1422,22 +1451,23 @@
       <c r="F26" s="6" t="n">
         <v>-336.1110270523728</v>
       </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía / Dirección General de Inversión Extranjera</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>26 de mayo de 2026</t>
         </is>
@@ -1445,9 +1475,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/downloads/indicadores/IED/IED_datos.xlsx
+++ b/downloads/indicadores/IED/IED_datos.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IED" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flujo trimestral" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acumulado comparable" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -495,21 +496,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Inversión Extranjera Directa (IED)</t>
+          <t>Inversión Extranjera Directa (IED) — Flujo trimestral</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE · Frecuencia: Trimestral · Unidad: Millones de dólares</t>
+          <t>Fuente: Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE · Frecuencia: Trimestral · Unidad: millones de dólares · Corte: Ene-Jun · Boletín: https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa · Fecha de publicación: 24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum · Fecha de publicación: 26 de mayo de 2026</t>
+          <t>URL del boletín / serie: https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa · Fecha de publicación: 24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -526,7 +527,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>IED acumulada</t>
+          <t>Flujo trimestral</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -546,7 +547,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Var. anual acumulada</t>
+          <t>Var. anual flujo</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -573,24 +574,16 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>1T-21</t>
+          <t>2T-99</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>44197</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>11864.03046282</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>2209.41801316</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>7025.211256549997</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>2629.401193109997</v>
-      </c>
+        <v>36251</v>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="8" t="inlineStr">
         <is>
@@ -604,36 +597,28 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2T-21</t>
+          <t>3T-99</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>44287</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>18433.46954255985</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>6025.000693990005</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>8658.214019469988</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>3750.254829099993</v>
-      </c>
+        <v>36342</v>
+      </c>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
       <c r="G7" s="10" t="n"/>
       <c r="H7" s="11" t="inlineStr">
         <is>
@@ -647,36 +632,28 @@
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>3T-21</t>
+          <t>4T-99</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>44378</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>24831.72427092007</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>9544.62750515</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>9999.422711059975</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>5287.674054709976</v>
-      </c>
+        <v>36434</v>
+      </c>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="8" t="inlineStr">
         <is>
@@ -690,36 +667,30 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>4T-21</t>
+          <t>1T-00</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>44470</v>
+        <v>36526</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>31621.20435087015</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>13825.30166943996</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>12213.01206093998</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>5582.890620490009</v>
-      </c>
+        <v>4600.64</v>
+      </c>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
       <c r="G9" s="10" t="n"/>
       <c r="H9" s="11" t="inlineStr">
         <is>
@@ -733,36 +704,30 @@
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>1T-22</t>
+          <t>2T-00</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>44562</v>
+        <v>36617</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>19427.45778673005</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>8792.209679979997</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>9259.124450750005</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>1376.123655999997</v>
-      </c>
+        <v>4857.42</v>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="8" t="inlineStr">
         <is>
@@ -776,36 +741,30 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2T-22</t>
+          <t>3T-00</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>44652</v>
+        <v>36708</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>27511.62373282995</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>11836.52779014</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>11655.60546753999</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>4019.490475149998</v>
-      </c>
+        <v>3056.95</v>
+      </c>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="11" t="inlineStr">
         <is>
@@ -819,36 +778,30 @@
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>3T-22</t>
+          <t>4T-00</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>44743</v>
+        <v>36800</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>32147.38886485986</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>14519.88582904002</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>14052.15139102999</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>3575.351644790012</v>
-      </c>
+        <v>5733.68</v>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
       <c r="G12" s="7" t="n"/>
       <c r="H12" s="8" t="inlineStr">
         <is>
@@ -862,37 +815,33 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>4T-22</t>
+          <t>1T-01</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>44835</v>
+        <v>36892</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>35291.61835650035</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>16993.09777798016</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>16027.79041017376</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>2270.730168346636</v>
-      </c>
-      <c r="G13" s="10" t="n"/>
+        <v>3598.68</v>
+      </c>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="10" t="n">
+        <v>-0.22</v>
+      </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -905,37 +854,33 @@
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>1T-23</t>
+          <t>2T-01</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>44927</v>
+        <v>36982</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>18635.69179056182</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>931.6891732793321</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>16704.7085712238</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>999.2940460586948</v>
-      </c>
-      <c r="G14" s="7" t="n"/>
+        <v>5218.83</v>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="7" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -948,37 +893,33 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2T-23</t>
+          <t>3T-01</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>45017</v>
+        <v>37073</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>29040.8238745911</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>2135.168038952664</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>22608.62151171782</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>4297.034323920598</v>
-      </c>
-      <c r="G15" s="10" t="n"/>
+        <v>16314.05</v>
+      </c>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="10" t="n">
+        <v>4.34</v>
+      </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -991,37 +932,33 @@
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3T-23</t>
+          <t>4T-01</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>45108</v>
+        <v>37165</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>32926.43680025823</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>2806.241495010777</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>24905.19143529355</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>5215.003869953881</v>
-      </c>
-      <c r="G16" s="7" t="n"/>
+        <v>4925.63</v>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="7" t="n">
+        <v>-0.14</v>
+      </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1034,37 +971,33 @@
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>4T-23</t>
+          <t>1T-02</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>45200</v>
+        <v>37257</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>36058.04377568115</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>4817.437436025721</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>26630.61271059473</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>4609.993629060474</v>
-      </c>
-      <c r="G17" s="10" t="n"/>
+        <v>5067.98</v>
+      </c>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="10" t="n">
+        <v>0.41</v>
+      </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1077,37 +1010,33 @@
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>1T-24</t>
+          <t>2T-02</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>45292</v>
+        <v>37347</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>20312.65875078067</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>599.3244456864041</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>19614.77618673003</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>98.5581183642047</v>
-      </c>
-      <c r="G18" s="7" t="n"/>
+        <v>6258.52</v>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="7" t="n">
+        <v>0.2</v>
+      </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1120,37 +1049,33 @@
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2T-24</t>
+          <t>3T-02</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>45383</v>
+        <v>37438</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>31096.32510957158</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>909.3070721249387</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>30287.60301161498</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>-100.5849741683989</v>
-      </c>
-      <c r="G19" s="10" t="n"/>
+        <v>6114.34</v>
+      </c>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="10" t="n">
+        <v>-0.63</v>
+      </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1163,37 +1088,33 @@
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3T-24</t>
+          <t>4T-02</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>45474</v>
+        <v>37530</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>35737.48954061164</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>2060.368951658199</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>30744.83932329829</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>2932.281265655119</v>
-      </c>
-      <c r="G20" s="7" t="n"/>
+        <v>6658.37</v>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="7" t="n">
+        <v>0.35</v>
+      </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1206,37 +1127,33 @@
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>4T-24</t>
+          <t>1T-03</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>45566</v>
+        <v>37622</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>36872.42195115965</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>3168.543654846584</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>28710.3148665372</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>4993.563429775793</v>
-      </c>
-      <c r="G21" s="10" t="n"/>
+        <v>3963.69</v>
+      </c>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="10" t="n">
+        <v>-0.22</v>
+      </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1249,37 +1166,33 @@
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>1T-25</t>
+          <t>2T-03</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>45658</v>
+        <v>37712</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>21373.19310550217</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>1586.396284871034</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>16646.99308879533</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>3139.80373183581</v>
-      </c>
-      <c r="G22" s="7" t="n"/>
+        <v>5547.34</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="7" t="n">
+        <v>-0.11</v>
+      </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1292,37 +1205,33 @@
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2T-25</t>
+          <t>3T-03</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>45748</v>
+        <v>37803</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>34264.56746296593</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>3148.538441297729</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>28914.10863011177</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>2201.920391556331</v>
-      </c>
-      <c r="G23" s="10" t="n"/>
+        <v>2521.68</v>
+      </c>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="10" t="n">
+        <v>-0.59</v>
+      </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1335,37 +1244,33 @@
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3T-25</t>
+          <t>4T-03</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>45839</v>
+        <v>37895</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>40905.61371637016</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>6563.38012553143</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>27748.84216433168</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>6593.391426507059</v>
-      </c>
-      <c r="G24" s="7" t="n"/>
+        <v>6217.27</v>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="7" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1378,37 +1283,33 @@
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>4T-25</t>
+          <t>1T-04</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>45931</v>
+        <v>37987</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>40870.76932803365</v>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>7377.426584413343</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>27649.33990823308</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>5844.002835387397</v>
-      </c>
-      <c r="G25" s="10" t="n"/>
+        <v>9363.459999999999</v>
+      </c>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="10" t="n">
+        <v>1.36</v>
+      </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1421,55 +1322,3489 @@
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>26 de mayo de 2026</t>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>2T-04</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>38078</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>4351.5</v>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="7" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>3T-04</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>38169</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>3284.91</v>
+      </c>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K27" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>4T-04</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>38261</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>8015.7</v>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>1T-05</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>38353</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>6761.62</v>
+      </c>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="10" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2T-05</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>38443</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>6773.62</v>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>3T-05</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>38534</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>5478.92</v>
+      </c>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>4T-05</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>38626</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>6781.66</v>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="7" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>1T-06</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>38718</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>7437.86</v>
+      </c>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>2T-06</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>38808</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>6634.31</v>
+      </c>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="7" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>3T-06</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>38899</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>2346.72</v>
+      </c>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="10" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>4T-06</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>38991</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>4817.96</v>
+      </c>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="7" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>1T-07</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>39083</v>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>10815.78</v>
+      </c>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>2T-07</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>39173</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>6137.64</v>
+      </c>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="7" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>3T-07</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>39264</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>7628.66</v>
+      </c>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K39" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>4T-07</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>39356</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>7811.96</v>
+      </c>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="7" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>1T-08</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>39448</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>8554.83</v>
+      </c>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="10" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K41" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2T-08</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>39539</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>8377.559999999999</v>
+      </c>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>3T-08</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>39630</v>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>5644.14</v>
+      </c>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="10" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K43" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>4T-08</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>39722</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>6945.7</v>
+      </c>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="7" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>1T-09</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>39814</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>6105.3</v>
+      </c>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="10" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K45" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2T-09</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>39904</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>6094.49</v>
+      </c>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="7" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>3T-09</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>39995</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>2398.04</v>
+      </c>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="10" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K47" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>4T-09</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>40087</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>3253.43</v>
+      </c>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="6" t="n"/>
+      <c r="G48" s="7" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>1T-10</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>40179</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>8722.790000000001</v>
+      </c>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K49" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>2T-10</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>40269</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>9301.620000000001</v>
+      </c>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>3T-10</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>40360</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>3942.08</v>
+      </c>
+      <c r="D51" s="9" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>4T-10</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>40452</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>5232.51</v>
+      </c>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="6" t="n"/>
+      <c r="G52" s="7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J52" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K52" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>1T-11</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>40544</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>8431.219999999999</v>
+      </c>
+      <c r="D53" s="9" t="n"/>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="9" t="n"/>
+      <c r="G53" s="10" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="H53" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>2T-11</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>40634</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>6697.45</v>
+      </c>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="6" t="n"/>
+      <c r="G54" s="7" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J54" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K54" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>3T-11</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>40725</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>4349.9</v>
+      </c>
+      <c r="D55" s="9" t="n"/>
+      <c r="E55" s="9" t="n"/>
+      <c r="F55" s="9" t="n"/>
+      <c r="G55" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K55" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>4T-11</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>40817</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>6154.01</v>
+      </c>
+      <c r="D56" s="6" t="n"/>
+      <c r="E56" s="6" t="n"/>
+      <c r="F56" s="6" t="n"/>
+      <c r="G56" s="7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>1T-12</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>40909</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>7893.19</v>
+      </c>
+      <c r="D57" s="9" t="n"/>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="9" t="n"/>
+      <c r="G57" s="10" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K57" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>2T-12</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>41000</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>5622.13</v>
+      </c>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="F58" s="6" t="n"/>
+      <c r="G58" s="7" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K58" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>3T-12</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>41091</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>5736.59</v>
+      </c>
+      <c r="D59" s="9" t="n"/>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="9" t="n"/>
+      <c r="G59" s="10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H59" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J59" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K59" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>4T-12</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>41183</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>2518.22</v>
+      </c>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n"/>
+      <c r="F60" s="6" t="n"/>
+      <c r="G60" s="7" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K60" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>1T-13</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>41275</v>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>10571.58</v>
+      </c>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="9" t="n"/>
+      <c r="G61" s="10" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J61" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K61" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>2T-13</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>41365</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>21019.15</v>
+      </c>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="6" t="n"/>
+      <c r="G62" s="7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J62" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K62" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>3T-13</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>41456</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>4179.16</v>
+      </c>
+      <c r="D63" s="9" t="n"/>
+      <c r="E63" s="9" t="n"/>
+      <c r="F63" s="9" t="n"/>
+      <c r="G63" s="10" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K63" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>4T-13</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>41548</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>12587.22</v>
+      </c>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="6" t="n"/>
+      <c r="G64" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J64" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K64" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>1T-14</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>41640</v>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>13828.01</v>
+      </c>
+      <c r="D65" s="9" t="n"/>
+      <c r="E65" s="9" t="n"/>
+      <c r="F65" s="9" t="n"/>
+      <c r="G65" s="10" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H65" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J65" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K65" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>2T-14</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>41730</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>5479.83</v>
+      </c>
+      <c r="D66" s="6" t="n"/>
+      <c r="E66" s="6" t="n"/>
+      <c r="F66" s="6" t="n"/>
+      <c r="G66" s="7" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J66" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K66" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>3T-14</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>41821</v>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>3222.12</v>
+      </c>
+      <c r="D67" s="9" t="n"/>
+      <c r="E67" s="9" t="n"/>
+      <c r="F67" s="9" t="n"/>
+      <c r="G67" s="10" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="H67" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J67" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K67" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>4T-14</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>41913</v>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>7822.45</v>
+      </c>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n"/>
+      <c r="F68" s="6" t="n"/>
+      <c r="G68" s="7" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J68" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K68" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>1T-15</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>42005</v>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>12136.46</v>
+      </c>
+      <c r="D69" s="9" t="n"/>
+      <c r="E69" s="9" t="n"/>
+      <c r="F69" s="9" t="n"/>
+      <c r="G69" s="10" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="H69" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K69" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>2T-15</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>42095</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>6656.85</v>
+      </c>
+      <c r="D70" s="6" t="n"/>
+      <c r="E70" s="6" t="n"/>
+      <c r="F70" s="6" t="n"/>
+      <c r="G70" s="7" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J70" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K70" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>3T-15</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>42186</v>
+      </c>
+      <c r="C71" s="9" t="n">
+        <v>9635.92</v>
+      </c>
+      <c r="D71" s="9" t="n"/>
+      <c r="E71" s="9" t="n"/>
+      <c r="F71" s="9" t="n"/>
+      <c r="G71" s="10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K71" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>4T-15</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>42278</v>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>7516.39</v>
+      </c>
+      <c r="D72" s="6" t="n"/>
+      <c r="E72" s="6" t="n"/>
+      <c r="F72" s="6" t="n"/>
+      <c r="G72" s="7" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J72" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K72" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>1T-16</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>42370</v>
+      </c>
+      <c r="C73" s="9" t="n">
+        <v>12805.81</v>
+      </c>
+      <c r="D73" s="9" t="n"/>
+      <c r="E73" s="9" t="n"/>
+      <c r="F73" s="9" t="n"/>
+      <c r="G73" s="10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H73" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>2T-16</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>42461</v>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>6210.67</v>
+      </c>
+      <c r="D74" s="6" t="n"/>
+      <c r="E74" s="6" t="n"/>
+      <c r="F74" s="6" t="n"/>
+      <c r="G74" s="7" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J74" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K74" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>3T-16</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>42552</v>
+      </c>
+      <c r="C75" s="9" t="n">
+        <v>4320.1</v>
+      </c>
+      <c r="D75" s="9" t="n"/>
+      <c r="E75" s="9" t="n"/>
+      <c r="F75" s="9" t="n"/>
+      <c r="G75" s="10" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="H75" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J75" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K75" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>4T-16</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>42644</v>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>7855.77</v>
+      </c>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="F76" s="6" t="n"/>
+      <c r="G76" s="7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J76" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K76" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>1T-17</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>42736</v>
+      </c>
+      <c r="C77" s="9" t="n">
+        <v>13796.27</v>
+      </c>
+      <c r="D77" s="9" t="n"/>
+      <c r="E77" s="9" t="n"/>
+      <c r="F77" s="9" t="n"/>
+      <c r="G77" s="10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H77" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J77" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K77" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>2T-17</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>42826</v>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>6837.92</v>
+      </c>
+      <c r="D78" s="6" t="n"/>
+      <c r="E78" s="6" t="n"/>
+      <c r="F78" s="6" t="n"/>
+      <c r="G78" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J78" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K78" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>3T-17</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>42917</v>
+      </c>
+      <c r="C79" s="9" t="n">
+        <v>6367.72</v>
+      </c>
+      <c r="D79" s="9" t="n"/>
+      <c r="E79" s="9" t="n"/>
+      <c r="F79" s="9" t="n"/>
+      <c r="G79" s="10" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H79" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J79" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K79" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>4T-17</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>43009</v>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>7062.67</v>
+      </c>
+      <c r="D80" s="6" t="n"/>
+      <c r="E80" s="6" t="n"/>
+      <c r="F80" s="6" t="n"/>
+      <c r="G80" s="7" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J80" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K80" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>1T-18</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>43101</v>
+      </c>
+      <c r="C81" s="9" t="n">
+        <v>14075.43</v>
+      </c>
+      <c r="D81" s="9" t="n"/>
+      <c r="E81" s="9" t="n"/>
+      <c r="F81" s="9" t="n"/>
+      <c r="G81" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H81" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K81" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>2T-18</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>43191</v>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>9579.73</v>
+      </c>
+      <c r="D82" s="6" t="n"/>
+      <c r="E82" s="6" t="n"/>
+      <c r="F82" s="6" t="n"/>
+      <c r="G82" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J82" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K82" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>3T-18</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>43282</v>
+      </c>
+      <c r="C83" s="9" t="n">
+        <v>4133.53</v>
+      </c>
+      <c r="D83" s="9" t="n"/>
+      <c r="E83" s="9" t="n"/>
+      <c r="F83" s="9" t="n"/>
+      <c r="G83" s="10" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J83" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K83" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>4T-18</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>43374</v>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>6325.44</v>
+      </c>
+      <c r="D84" s="6" t="n"/>
+      <c r="E84" s="6" t="n"/>
+      <c r="F84" s="6" t="n"/>
+      <c r="G84" s="7" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J84" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K84" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C85" s="9" t="n">
+        <v>15213.12</v>
+      </c>
+      <c r="D85" s="9" t="n"/>
+      <c r="E85" s="9" t="n"/>
+      <c r="F85" s="9" t="n"/>
+      <c r="G85" s="10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H85" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K85" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>2T-19</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>43556</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>6681.61</v>
+      </c>
+      <c r="D86" s="6" t="n"/>
+      <c r="E86" s="6" t="n"/>
+      <c r="F86" s="6" t="n"/>
+      <c r="G86" s="7" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J86" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K86" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>3T-19</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>43647</v>
+      </c>
+      <c r="C87" s="9" t="n">
+        <v>8218.74</v>
+      </c>
+      <c r="D87" s="9" t="n"/>
+      <c r="E87" s="9" t="n"/>
+      <c r="F87" s="9" t="n"/>
+      <c r="G87" s="10" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J87" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K87" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>4T-19</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>43739</v>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>4685.06</v>
+      </c>
+      <c r="D88" s="6" t="n"/>
+      <c r="E88" s="6" t="n"/>
+      <c r="F88" s="6" t="n"/>
+      <c r="G88" s="7" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J88" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K88" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C89" s="9" t="n">
+        <v>16783.71</v>
+      </c>
+      <c r="D89" s="9" t="n"/>
+      <c r="E89" s="9" t="n"/>
+      <c r="F89" s="9" t="n"/>
+      <c r="G89" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H89" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J89" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K89" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>2T-20</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>43922</v>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>7377.65</v>
+      </c>
+      <c r="D90" s="6" t="n"/>
+      <c r="E90" s="6" t="n"/>
+      <c r="F90" s="6" t="n"/>
+      <c r="G90" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J90" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K90" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>3T-20</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>44013</v>
+      </c>
+      <c r="C91" s="9" t="n">
+        <v>1339.34</v>
+      </c>
+      <c r="D91" s="9" t="n"/>
+      <c r="E91" s="9" t="n"/>
+      <c r="F91" s="9" t="n"/>
+      <c r="G91" s="10" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="H91" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J91" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K91" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>4T-20</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>44105</v>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>2783.55</v>
+      </c>
+      <c r="D92" s="6" t="n"/>
+      <c r="E92" s="6" t="n"/>
+      <c r="F92" s="6" t="n"/>
+      <c r="G92" s="7" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J92" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K92" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C93" s="9" t="n">
+        <v>16503.34</v>
+      </c>
+      <c r="D93" s="9" t="n"/>
+      <c r="E93" s="9" t="n"/>
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="10" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="H93" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J93" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K93" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>2T-21</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>44287</v>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>5927.4</v>
+      </c>
+      <c r="D94" s="6" t="n"/>
+      <c r="E94" s="6" t="n"/>
+      <c r="F94" s="6" t="n"/>
+      <c r="G94" s="7" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I94" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J94" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K94" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>3T-21</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>44378</v>
+      </c>
+      <c r="C95" s="9" t="n">
+        <v>6439.84</v>
+      </c>
+      <c r="D95" s="9" t="n"/>
+      <c r="E95" s="9" t="n"/>
+      <c r="F95" s="9" t="n"/>
+      <c r="G95" s="10" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="H95" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J95" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K95" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>4T-21</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>44470</v>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>4984.47</v>
+      </c>
+      <c r="D96" s="6" t="n"/>
+      <c r="E96" s="6" t="n"/>
+      <c r="F96" s="6" t="n"/>
+      <c r="G96" s="7" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I96" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J96" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K96" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C97" s="9" t="n">
+        <v>22783.26</v>
+      </c>
+      <c r="D97" s="9" t="n"/>
+      <c r="E97" s="9" t="n"/>
+      <c r="F97" s="9" t="n"/>
+      <c r="G97" s="10" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H97" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J97" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K97" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>2T-22</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>44652</v>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>8382.120000000001</v>
+      </c>
+      <c r="D98" s="6" t="n"/>
+      <c r="E98" s="6" t="n"/>
+      <c r="F98" s="6" t="n"/>
+      <c r="G98" s="7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I98" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J98" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K98" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>3T-22</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>44743</v>
+      </c>
+      <c r="C99" s="9" t="n">
+        <v>3450.38</v>
+      </c>
+      <c r="D99" s="9" t="n"/>
+      <c r="E99" s="9" t="n"/>
+      <c r="F99" s="9" t="n"/>
+      <c r="G99" s="10" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>4T-22</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>44835</v>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>1804.83</v>
+      </c>
+      <c r="D100" s="6" t="n"/>
+      <c r="E100" s="6" t="n"/>
+      <c r="F100" s="6" t="n"/>
+      <c r="G100" s="7" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J100" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K100" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C101" s="9" t="n">
+        <v>23658.92</v>
+      </c>
+      <c r="D101" s="9" t="n"/>
+      <c r="E101" s="9" t="n"/>
+      <c r="F101" s="9" t="n"/>
+      <c r="G101" s="10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H101" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J101" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K101" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>2T-23</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>45017</v>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>8512.41</v>
+      </c>
+      <c r="D102" s="6" t="n"/>
+      <c r="E102" s="6" t="n"/>
+      <c r="F102" s="6" t="n"/>
+      <c r="G102" s="7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I102" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J102" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K102" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>3T-23</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>45108</v>
+      </c>
+      <c r="C103" s="9" t="n">
+        <v>3043.69</v>
+      </c>
+      <c r="D103" s="9" t="n"/>
+      <c r="E103" s="9" t="n"/>
+      <c r="F103" s="9" t="n"/>
+      <c r="G103" s="10" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="H103" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J103" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K103" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>4T-23</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>45200</v>
+      </c>
+      <c r="C104" s="6" t="n">
+        <v>1292.36</v>
+      </c>
+      <c r="D104" s="6" t="n"/>
+      <c r="E104" s="6" t="n"/>
+      <c r="F104" s="6" t="n"/>
+      <c r="G104" s="7" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I104" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J104" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K104" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C105" s="9" t="n">
+        <v>27218.64</v>
+      </c>
+      <c r="D105" s="9" t="n"/>
+      <c r="E105" s="9" t="n"/>
+      <c r="F105" s="9" t="n"/>
+      <c r="G105" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K105" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>2T-24</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>45383</v>
+      </c>
+      <c r="C106" s="6" t="n">
+        <v>6490.68</v>
+      </c>
+      <c r="D106" s="6" t="n"/>
+      <c r="E106" s="6" t="n"/>
+      <c r="F106" s="6" t="n"/>
+      <c r="G106" s="7" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J106" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K106" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>3T-24</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>45474</v>
+      </c>
+      <c r="C107" s="9" t="n">
+        <v>3075.28</v>
+      </c>
+      <c r="D107" s="9" t="n"/>
+      <c r="E107" s="9" t="n"/>
+      <c r="F107" s="9" t="n"/>
+      <c r="G107" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J107" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K107" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>4T-24</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>45566</v>
+      </c>
+      <c r="C108" s="6" t="n">
+        <v>1184.56</v>
+      </c>
+      <c r="D108" s="6" t="n"/>
+      <c r="E108" s="6" t="n"/>
+      <c r="F108" s="6" t="n"/>
+      <c r="G108" s="7" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I108" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J108" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K108" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C109" s="9" t="n">
+        <v>24061.16</v>
+      </c>
+      <c r="D109" s="9" t="n"/>
+      <c r="E109" s="9" t="n"/>
+      <c r="F109" s="9" t="n"/>
+      <c r="G109" s="10" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="H109" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J109" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K109" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>2T-25</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C110" s="6" t="n">
+        <v>13958.56</v>
+      </c>
+      <c r="D110" s="6" t="n"/>
+      <c r="E110" s="6" t="n"/>
+      <c r="F110" s="6" t="n"/>
+      <c r="G110" s="7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I110" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J110" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K110" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>3T-25</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C111" s="9" t="n">
+        <v>7886.47</v>
+      </c>
+      <c r="D111" s="9" t="n"/>
+      <c r="E111" s="9" t="n"/>
+      <c r="F111" s="9" t="n"/>
+      <c r="G111" s="10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H111" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J111" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K111" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>4T-25</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C112" s="6" t="n">
+        <v>-3989.51</v>
+      </c>
+      <c r="D112" s="6" t="n"/>
+      <c r="E112" s="6" t="n"/>
+      <c r="F112" s="6" t="n"/>
+      <c r="G112" s="7" t="n">
+        <v>-4.37</v>
+      </c>
+      <c r="H112" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I112" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J112" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K112" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
           <t>1T-26</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B113" s="5" t="n">
         <v>46023</v>
       </c>
-      <c r="C26" s="6" t="n">
-        <v>23590.62204554513</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>1705.227100742525</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>22221.50597185501</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>-336.1110270523728</v>
-      </c>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
-        </is>
-      </c>
-      <c r="J26" s="8" t="inlineStr">
-        <is>
-          <t>https://www.presidenta.gob.mx/boletines/inversion-extranjera-aumenta-10-4-por-ciento-en-primer-trimestre-2026-presidenta-sheinbaum</t>
-        </is>
-      </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>26 de mayo de 2026</t>
+      <c r="C113" s="9" t="n">
+        <v>24503.05</v>
+      </c>
+      <c r="D113" s="9" t="n"/>
+      <c r="E113" s="9" t="n"/>
+      <c r="F113" s="9" t="n"/>
+      <c r="G113" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J113" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K113" s="11" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>2T-26</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C114" s="6" t="n">
+        <v>10464.95</v>
+      </c>
+      <c r="D114" s="6" t="n">
+        <v>654.37</v>
+      </c>
+      <c r="E114" s="6" t="n">
+        <v>6870.96</v>
+      </c>
+      <c r="F114" s="6" t="n">
+        <v>2939.62</v>
+      </c>
+      <c r="G114" s="7" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="I114" s="8" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE</t>
+        </is>
+      </c>
+      <c r="J114" s="8" t="inlineStr">
+        <is>
+          <t>https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa</t>
+        </is>
+      </c>
+      <c r="K114" s="8" t="inlineStr">
+        <is>
+          <t>24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1481,4 +4816,682 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Inversión Extranjera Directa (IED) — Acumulado al mismo corte de cada año (Ene-Jun)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Fuente: Secretaría de Economía — Dirección General de Inversión Extranjera / RNIE · Frecuencia: Trimestral · Unidad: millones de dólares · Boletín: https://www.gob.mx/se/acciones-y-programas/competitividad-y-normatividad-inversion-extranjera-directa · Fecha de publicación: 24 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Solo se incluye el corte Ene-Jun de cada año para mantener la comparabilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Corte</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>IED acumulada</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Nuevas inversiones</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Reinversión de utilidades</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Cuentas entre compañías</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Var. anual acumulada</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 99</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>6991.97</v>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 00</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>9458.059999999999</v>
+      </c>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="10" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 01</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>8817.51</v>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="7" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 02</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>11326.5</v>
+      </c>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="10" t="n">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 03</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>9511.02</v>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="7" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 04</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>13714.95</v>
+      </c>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="10" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 05</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>13535.24</v>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="7" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 06</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>14072.17</v>
+      </c>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="10" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 07</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>16953.42</v>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="7" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 08</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>16932.4</v>
+      </c>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="10" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 09</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>12199.79</v>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="7" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 10</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>18024.41</v>
+      </c>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="10" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 11</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>15128.67</v>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="7" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 12</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>13515.32</v>
+      </c>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="10" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 13</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>31590.73</v>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="7" t="n">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 14</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>19307.83</v>
+      </c>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="10" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 15</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>18793.31</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="7" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 16</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>19016.48</v>
+      </c>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="10" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 17</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>20634.18</v>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="7" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 18</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>23655.16</v>
+      </c>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="10" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 19</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>21894.73</v>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="7" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 20</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>24161.35</v>
+      </c>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="10" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 21</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>22430.74</v>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="7" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 22</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>31165.38</v>
+      </c>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="10" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 23</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>32171.33</v>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="7" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 24</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>33709.33</v>
+      </c>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="10" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 25</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>38019.72</v>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="7" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Ene-Jun 26</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>34968</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>2726</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>30957</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>1285</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>